--- a/architectures and decision enablers/architecture decision enabler/iso-27001-threat-assessment/ISO_27001_Security_Assessment.xlsx
+++ b/architectures and decision enablers/architecture decision enabler/iso-27001-threat-assessment/ISO_27001_Security_Assessment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amitp\Documents\portfolio-repo\architectures and decision enablers\architecture decision enabler\iso-27001-threat-assessment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Amit\eBooks\Interview Quick Rampup\Fractional Architect Consulting &amp; Freelancing\UPWORK &amp; TOPMATE FILES AND PRODUCTS\ISO27001_SECURITY_ASSESSMENT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80F27DE-F8E0-464D-A86F-3D893FE6566F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA51555-B993-42EA-A07A-E7CEEE36DED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D62D5DFD-F87A-4D1C-B4C2-9718B4BFE1A3}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="123">
   <si>
     <t>Category</t>
   </si>
@@ -1852,12 +1852,15 @@
   <si>
     <t>Security Assessment State</t>
   </si>
+  <si>
+    <t>© 2026 Amit Kulkarni. All rights reserved.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1940,6 +1943,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1989,7 +2000,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2028,19 +2039,11 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2054,11 +2057,158 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFDCDFE5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="8"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color theme="8"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2091,128 +2241,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color theme="8"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="8"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFDCDFE5"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
@@ -2242,7 +2270,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[ISO_27001_Security_Assessment.xlsx]Results!PivotTable2</c:name>
+    <c:name>[ISO_27001_Security_Assess.xlsx]Results!PivotTable2</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -3688,13 +3716,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E73E7247-BCFC-4015-986D-687DB3B658AD}" name="Table1" displayName="Table1" ref="A1:D76" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E73E7247-BCFC-4015-986D-687DB3B658AD}" name="Table1" displayName="Table1" ref="A1:D76" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
   <autoFilter ref="A1:D76" xr:uid="{E73E7247-BCFC-4015-986D-687DB3B658AD}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4040D9CC-679B-4FB9-95A0-A62DC347ACB8}" name="Category" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{97669469-615B-4885-AA0A-9DEFB223083F}" name="Client-Specific Question" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{1249DB9C-8244-4777-AB25-41AD08B48F14}" name="User Priority" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{20D94323-F57F-4A2B-A9AC-BD5E52F0997A}" name="User Score" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{4040D9CC-679B-4FB9-95A0-A62DC347ACB8}" name="Category" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{97669469-615B-4885-AA0A-9DEFB223083F}" name="Client-Specific Question" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{1249DB9C-8244-4777-AB25-41AD08B48F14}" name="User Priority" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{20D94323-F57F-4A2B-A9AC-BD5E52F0997A}" name="User Score" dataDxfId="1">
       <calculatedColumnFormula array="1">_xlfn.SWITCH(C2,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3716,12 +3744,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E732D738-18CD-454A-B682-480D9C362FF3}" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="3" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E732D738-18CD-454A-B682-480D9C362FF3}" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8">
   <autoFilter ref="A1:C5" xr:uid="{E732D738-18CD-454A-B682-480D9C362FF3}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{6C99AD2D-6C3E-4777-9C93-769BB389F17B}" name="States"/>
-    <tableColumn id="2" xr3:uid="{99472FA6-7E3F-4662-9A23-747AF2E8E183}" name="Definitions" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{271029AC-1612-4193-95C8-4170F042EB18}" name="Operational Impact" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{99472FA6-7E3F-4662-9A23-747AF2E8E183}" name="Definitions" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{271029AC-1612-4193-95C8-4170F042EB18}" name="Operational Impact" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4055,12 +4083,12 @@
       <c r="B2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="22" cm="1">
+      <c r="C2" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="24" cm="1">
         <f t="array" ref="D2">_xlfn.SWITCH(C2,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="93.6" x14ac:dyDescent="0.35">
@@ -4070,12 +4098,12 @@
       <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="22" cm="1">
+      <c r="C3" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="24" cm="1">
         <f t="array" ref="D3">_xlfn.SWITCH(C3,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="93.6" x14ac:dyDescent="0.35">
@@ -4085,10 +4113,10 @@
       <c r="B4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="22" cm="1">
+      <c r="D4" s="24" cm="1">
         <f t="array" ref="D4">_xlfn.SWITCH(C4,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4100,10 +4128,10 @@
       <c r="B5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="22" cm="1">
+      <c r="D5" s="24" cm="1">
         <f t="array" ref="D5">_xlfn.SWITCH(C5,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4115,10 +4143,10 @@
       <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="22" cm="1">
+      <c r="D6" s="24" cm="1">
         <f t="array" ref="D6">_xlfn.SWITCH(C6,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4130,10 +4158,10 @@
       <c r="B7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="22" cm="1">
+      <c r="D7" s="24" cm="1">
         <f t="array" ref="D7">_xlfn.SWITCH(C7,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4145,12 +4173,12 @@
       <c r="B8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="22" cm="1">
+      <c r="C8" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="24" cm="1">
         <f t="array" ref="D8">_xlfn.SWITCH(C8,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="93.6" x14ac:dyDescent="0.3">
@@ -4160,12 +4188,12 @@
       <c r="B9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="22" cm="1">
+      <c r="C9" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="24" cm="1">
         <f t="array" ref="D9">_xlfn.SWITCH(C9,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="93.6" x14ac:dyDescent="0.3">
@@ -4175,12 +4203,12 @@
       <c r="B10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="22" cm="1">
+      <c r="C10" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="24" cm="1">
         <f t="array" ref="D10">_xlfn.SWITCH(C10,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="109.2" x14ac:dyDescent="0.3">
@@ -4190,10 +4218,10 @@
       <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="22" cm="1">
+      <c r="D11" s="24" cm="1">
         <f t="array" ref="D11">_xlfn.SWITCH(C11,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4205,10 +4233,10 @@
       <c r="B12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="22" cm="1">
+      <c r="D12" s="24" cm="1">
         <f t="array" ref="D12">_xlfn.SWITCH(C12,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4220,10 +4248,10 @@
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="22" cm="1">
+      <c r="D13" s="24" cm="1">
         <f t="array" ref="D13">_xlfn.SWITCH(C13,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4235,12 +4263,12 @@
       <c r="B14" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="22" cm="1">
+      <c r="C14" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="24" cm="1">
         <f t="array" ref="D14">_xlfn.SWITCH(C14,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4250,12 +4278,12 @@
       <c r="B15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="22" cm="1">
+      <c r="C15" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="24" cm="1">
         <f t="array" ref="D15">_xlfn.SWITCH(C15,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4265,12 +4293,12 @@
       <c r="B16" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="22" cm="1">
+      <c r="C16" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="24" cm="1">
         <f t="array" ref="D16">_xlfn.SWITCH(C16,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4280,12 +4308,12 @@
       <c r="B17" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="22" cm="1">
+      <c r="C17" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="24" cm="1">
         <f t="array" ref="D17">_xlfn.SWITCH(C17,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="100.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -4295,12 +4323,12 @@
       <c r="B18" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="22" cm="1">
+      <c r="C18" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="24" cm="1">
         <f t="array" ref="D18">_xlfn.SWITCH(C18,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="109.8" x14ac:dyDescent="0.35">
@@ -4310,27 +4338,27 @@
       <c r="B19" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="22" cm="1">
+      <c r="C19" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="24" cm="1">
         <f t="array" ref="D19">_xlfn.SWITCH(C19,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="109.8" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="22" cm="1">
+      <c r="C20" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="24" cm="1">
         <f t="array" ref="D20">_xlfn.SWITCH(C20,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4340,10 +4368,10 @@
       <c r="B21" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="22" cm="1">
+      <c r="D21" s="24" cm="1">
         <f t="array" ref="D21">_xlfn.SWITCH(C21,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4355,10 +4383,10 @@
       <c r="B22" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="22" cm="1">
+      <c r="D22" s="24" cm="1">
         <f t="array" ref="D22">_xlfn.SWITCH(C22,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4370,10 +4398,10 @@
       <c r="B23" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="22" cm="1">
+      <c r="D23" s="24" cm="1">
         <f t="array" ref="D23">_xlfn.SWITCH(C23,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4385,12 +4413,12 @@
       <c r="B24" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="22" cm="1">
+      <c r="C24" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="24" cm="1">
         <f t="array" ref="D24">_xlfn.SWITCH(C24,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="109.8" x14ac:dyDescent="0.35">
@@ -4400,12 +4428,12 @@
       <c r="B25" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="22" cm="1">
+      <c r="C25" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="24" cm="1">
         <f t="array" ref="D25">_xlfn.SWITCH(C25,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="96.6" customHeight="1" x14ac:dyDescent="0.35">
@@ -4415,10 +4443,10 @@
       <c r="B26" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="22" cm="1">
+      <c r="D26" s="24" cm="1">
         <f t="array" ref="D26">_xlfn.SWITCH(C26,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4430,12 +4458,12 @@
       <c r="B27" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="22" cm="1">
+      <c r="C27" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="24" cm="1">
         <f t="array" ref="D27">_xlfn.SWITCH(C27,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="105.6" customHeight="1" x14ac:dyDescent="0.35">
@@ -4445,10 +4473,10 @@
       <c r="B28" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="22" cm="1">
+      <c r="D28" s="24" cm="1">
         <f t="array" ref="D28">_xlfn.SWITCH(C28,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4460,12 +4488,12 @@
       <c r="B29" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="22" cm="1">
+      <c r="C29" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="24" cm="1">
         <f t="array" ref="D29">_xlfn.SWITCH(C29,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="109.8" x14ac:dyDescent="0.35">
@@ -4475,12 +4503,12 @@
       <c r="B30" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="22" cm="1">
+      <c r="C30" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="24" cm="1">
         <f t="array" ref="D30">_xlfn.SWITCH(C30,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="115.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -4490,12 +4518,12 @@
       <c r="B31" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" s="22" cm="1">
+      <c r="C31" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="24" cm="1">
         <f t="array" ref="D31">_xlfn.SWITCH(C31,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="122.4" customHeight="1" x14ac:dyDescent="0.35">
@@ -4505,12 +4533,12 @@
       <c r="B32" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="22" cm="1">
+      <c r="C32" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="24" cm="1">
         <f t="array" ref="D32">_xlfn.SWITCH(C32,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="106.8" customHeight="1" x14ac:dyDescent="0.35">
@@ -4520,12 +4548,12 @@
       <c r="B33" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="22" cm="1">
+      <c r="C33" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="24" cm="1">
         <f t="array" ref="D33">_xlfn.SWITCH(C33,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="104.4" customHeight="1" x14ac:dyDescent="0.35">
@@ -4535,12 +4563,12 @@
       <c r="B34" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" s="22" cm="1">
+      <c r="C34" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="24" cm="1">
         <f t="array" ref="D34">_xlfn.SWITCH(C34,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="100.8" customHeight="1" x14ac:dyDescent="0.35">
@@ -4550,10 +4578,10 @@
       <c r="B35" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D35" s="22" cm="1">
+      <c r="D35" s="24" cm="1">
         <f t="array" ref="D35">_xlfn.SWITCH(C35,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4565,10 +4593,10 @@
       <c r="B36" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D36" s="22" cm="1">
+      <c r="D36" s="24" cm="1">
         <f t="array" ref="D36">_xlfn.SWITCH(C36,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4580,12 +4608,12 @@
       <c r="B37" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="22" cm="1">
+      <c r="C37" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="24" cm="1">
         <f t="array" ref="D37">_xlfn.SWITCH(C37,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="109.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -4595,12 +4623,12 @@
       <c r="B38" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" s="22" cm="1">
+      <c r="C38" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="24" cm="1">
         <f t="array" ref="D38">_xlfn.SWITCH(C38,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="100.8" customHeight="1" x14ac:dyDescent="0.35">
@@ -4610,12 +4638,12 @@
       <c r="B39" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D39" s="22" cm="1">
+      <c r="C39" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="24" cm="1">
         <f t="array" ref="D39">_xlfn.SWITCH(C39,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="108" customHeight="1" x14ac:dyDescent="0.35">
@@ -4625,10 +4653,10 @@
       <c r="B40" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D40" s="22" cm="1">
+      <c r="D40" s="24" cm="1">
         <f t="array" ref="D40">_xlfn.SWITCH(C40,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4640,10 +4668,10 @@
       <c r="B41" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D41" s="22" cm="1">
+      <c r="D41" s="24" cm="1">
         <f t="array" ref="D41">_xlfn.SWITCH(C41,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4655,12 +4683,12 @@
       <c r="B42" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" s="22" cm="1">
+      <c r="C42" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="24" cm="1">
         <f t="array" ref="D42">_xlfn.SWITCH(C42,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="127.8" customHeight="1" x14ac:dyDescent="0.35">
@@ -4670,12 +4698,12 @@
       <c r="B43" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="22" cm="1">
+      <c r="C43" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="24" cm="1">
         <f t="array" ref="D43">_xlfn.SWITCH(C43,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="111" customHeight="1" x14ac:dyDescent="0.35">
@@ -4685,12 +4713,12 @@
       <c r="B44" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="22" cm="1">
+      <c r="C44" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="24" cm="1">
         <f t="array" ref="D44">_xlfn.SWITCH(C44,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="110.4" customHeight="1" x14ac:dyDescent="0.35">
@@ -4700,12 +4728,12 @@
       <c r="B45" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" s="22" cm="1">
+      <c r="C45" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="24" cm="1">
         <f t="array" ref="D45">_xlfn.SWITCH(C45,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="136.19999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -4715,12 +4743,12 @@
       <c r="B46" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" s="22" cm="1">
+      <c r="C46" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="24" cm="1">
         <f t="array" ref="D46">_xlfn.SWITCH(C46,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="105" customHeight="1" x14ac:dyDescent="0.35">
@@ -4730,12 +4758,12 @@
       <c r="B47" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D47" s="22" cm="1">
+      <c r="C47" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="24" cm="1">
         <f t="array" ref="D47">_xlfn.SWITCH(C47,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="104.4" customHeight="1" x14ac:dyDescent="0.35">
@@ -4745,12 +4773,12 @@
       <c r="B48" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D48" s="22" cm="1">
+      <c r="C48" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="24" cm="1">
         <f t="array" ref="D48">_xlfn.SWITCH(C48,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="124.8" customHeight="1" x14ac:dyDescent="0.35">
@@ -4760,10 +4788,10 @@
       <c r="B49" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D49" s="22" cm="1">
+      <c r="D49" s="24" cm="1">
         <f t="array" ref="D49">_xlfn.SWITCH(C49,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4775,12 +4803,12 @@
       <c r="B50" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="22" cm="1">
+      <c r="C50" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="24" cm="1">
         <f t="array" ref="D50">_xlfn.SWITCH(C50,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="111" customHeight="1" x14ac:dyDescent="0.35">
@@ -4790,10 +4818,10 @@
       <c r="B51" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D51" s="22" cm="1">
+      <c r="D51" s="24" cm="1">
         <f t="array" ref="D51">_xlfn.SWITCH(C51,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4805,10 +4833,10 @@
       <c r="B52" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D52" s="22" cm="1">
+      <c r="D52" s="24" cm="1">
         <f t="array" ref="D52">_xlfn.SWITCH(C52,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4820,10 +4848,10 @@
       <c r="B53" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D53" s="22" cm="1">
+      <c r="D53" s="24" cm="1">
         <f t="array" ref="D53">_xlfn.SWITCH(C53,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4835,10 +4863,10 @@
       <c r="B54" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D54" s="22" cm="1">
+      <c r="D54" s="24" cm="1">
         <f t="array" ref="D54">_xlfn.SWITCH(C54,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4850,10 +4878,10 @@
       <c r="B55" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D55" s="22" cm="1">
+      <c r="D55" s="24" cm="1">
         <f t="array" ref="D55">_xlfn.SWITCH(C55,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4865,12 +4893,12 @@
       <c r="B56" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D56" s="22" cm="1">
+      <c r="C56" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" s="24" cm="1">
         <f t="array" ref="D56">_xlfn.SWITCH(C56,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="106.8" customHeight="1" x14ac:dyDescent="0.35">
@@ -4880,10 +4908,10 @@
       <c r="B57" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D57" s="22" cm="1">
+      <c r="D57" s="24" cm="1">
         <f t="array" ref="D57">_xlfn.SWITCH(C57,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4895,10 +4923,10 @@
       <c r="B58" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D58" s="22" cm="1">
+      <c r="D58" s="24" cm="1">
         <f t="array" ref="D58">_xlfn.SWITCH(C58,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4910,10 +4938,10 @@
       <c r="B59" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D59" s="22" cm="1">
+      <c r="D59" s="24" cm="1">
         <f t="array" ref="D59">_xlfn.SWITCH(C59,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4925,10 +4953,10 @@
       <c r="B60" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="22" cm="1">
+      <c r="D60" s="24" cm="1">
         <f t="array" ref="D60">_xlfn.SWITCH(C60,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4940,10 +4968,10 @@
       <c r="B61" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D61" s="22" cm="1">
+      <c r="D61" s="24" cm="1">
         <f t="array" ref="D61">_xlfn.SWITCH(C61,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4955,10 +4983,10 @@
       <c r="B62" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D62" s="22" cm="1">
+      <c r="D62" s="24" cm="1">
         <f t="array" ref="D62">_xlfn.SWITCH(C62,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -4970,10 +4998,10 @@
       <c r="B63" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D63" s="22" cm="1">
+      <c r="D63" s="24" cm="1">
         <f t="array" ref="D63">_xlfn.SWITCH(C63,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4985,10 +5013,10 @@
       <c r="B64" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D64" s="22" cm="1">
+      <c r="D64" s="24" cm="1">
         <f t="array" ref="D64">_xlfn.SWITCH(C64,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -5000,12 +5028,12 @@
       <c r="B65" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D65" s="22" cm="1">
+      <c r="C65" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" s="24" cm="1">
         <f t="array" ref="D65">_xlfn.SWITCH(C65,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="105" customHeight="1" x14ac:dyDescent="0.35">
@@ -5015,10 +5043,10 @@
       <c r="B66" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D66" s="22" cm="1">
+      <c r="D66" s="24" cm="1">
         <f t="array" ref="D66">_xlfn.SWITCH(C66,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -5030,12 +5058,12 @@
       <c r="B67" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D67" s="22" cm="1">
+      <c r="C67" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="24" cm="1">
         <f t="array" ref="D67">_xlfn.SWITCH(C67,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="113.4" customHeight="1" x14ac:dyDescent="0.35">
@@ -5045,10 +5073,10 @@
       <c r="B68" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D68" s="22" cm="1">
+      <c r="D68" s="24" cm="1">
         <f t="array" ref="D68">_xlfn.SWITCH(C68,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -5060,10 +5088,10 @@
       <c r="B69" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D69" s="22" cm="1">
+      <c r="D69" s="24" cm="1">
         <f t="array" ref="D69">_xlfn.SWITCH(C69,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -5075,10 +5103,10 @@
       <c r="B70" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D70" s="22" cm="1">
+      <c r="D70" s="24" cm="1">
         <f t="array" ref="D70">_xlfn.SWITCH(C70,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -5090,10 +5118,10 @@
       <c r="B71" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D71" s="22" cm="1">
+      <c r="D71" s="24" cm="1">
         <f t="array" ref="D71">_xlfn.SWITCH(C71,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -5105,10 +5133,10 @@
       <c r="B72" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D72" s="22" cm="1">
+      <c r="D72" s="24" cm="1">
         <f t="array" ref="D72">_xlfn.SWITCH(C72,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -5120,10 +5148,10 @@
       <c r="B73" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D73" s="22" cm="1">
+      <c r="D73" s="24" cm="1">
         <f t="array" ref="D73">_xlfn.SWITCH(C73,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -5135,10 +5163,10 @@
       <c r="B74" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D74" s="22" cm="1">
+      <c r="D74" s="24" cm="1">
         <f t="array" ref="D74">_xlfn.SWITCH(C74,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.5</v>
       </c>
@@ -5150,10 +5178,10 @@
       <c r="B75" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D75" s="22" cm="1">
+      <c r="D75" s="24" cm="1">
         <f t="array" ref="D75">_xlfn.SWITCH(C75,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -5165,18 +5193,24 @@
       <c r="B76" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D76" s="22" cm="1">
+      <c r="C76" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="24" cm="1">
         <f t="array" ref="D76">_xlfn.SWITCH(C76,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="25.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B79" s="7"/>
       <c r="C79" s="2"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="Bxw6tzwbKjvhy4zlwArCpV9zEyuCB9Li8uD50RZaFXrNyOE4H9BN6xFUvmNlxtqQj5gZPBmaWD097lsoWyCaFA==" saltValue="uulmoAE9LkFJrdMVz5cEAQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataValidations xWindow="1284" yWindow="779" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Select Organization Response" prompt="Select 1 out of A,B,C,D" sqref="C2:C76" xr:uid="{38769ACA-BE52-4C22-A94E-0EFE0281E8FE}">
       <formula1>"A,B,C,D"</formula1>
@@ -5192,7 +5226,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6992F667-9237-424C-9FAB-1605BDA91A9B}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="71.6640625" customWidth="1"/>
@@ -5220,174 +5254,174 @@
       <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="25">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A2, User_Responses!$D$2:$D$76)</f>
-        <v>0.7</v>
-      </c>
-      <c r="C2" s="20">
+        <v>0.9</v>
+      </c>
+      <c r="C2" s="18">
         <v>3</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="26">
         <f>B2*C2</f>
-        <v>2.0999999999999996</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="25">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A3, User_Responses!$D$2:$D$76)</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="C3" s="20">
+        <v>0.7</v>
+      </c>
+      <c r="C3" s="18">
         <v>3</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="26">
         <f t="shared" ref="D3:D15" si="0">B3*C3</f>
-        <v>1.6500000000000001</v>
+        <v>2.0999999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="25">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A4, User_Responses!$D$2:$D$76)</f>
-        <v>0.7</v>
-      </c>
-      <c r="C4" s="20">
+        <v>1</v>
+      </c>
+      <c r="C4" s="18">
         <v>3</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="26">
         <f t="shared" si="0"/>
-        <v>2.0999999999999996</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="25">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A5, User_Responses!$D$2:$D$76)</f>
-        <v>0.8</v>
-      </c>
-      <c r="C5" s="20">
+        <v>0.85</v>
+      </c>
+      <c r="C5" s="18">
         <v>3</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="26">
         <f t="shared" si="0"/>
-        <v>2.4000000000000004</v>
+        <v>2.5499999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="25">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A6, User_Responses!$D$2:$D$76)</f>
-        <v>0.45</v>
-      </c>
-      <c r="C6" s="20">
+        <v>0.65</v>
+      </c>
+      <c r="C6" s="18">
         <v>2</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="26">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="25">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A7, User_Responses!$D$2:$D$76)</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="C7" s="20">
+        <v>0.85</v>
+      </c>
+      <c r="C7" s="18">
         <v>2</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="26">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="25">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A8, User_Responses!$D$2:$D$76)</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="C8" s="20">
+        <v>0.85</v>
+      </c>
+      <c r="C8" s="18">
         <v>2</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="26">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="25">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A9, User_Responses!$D$2:$D$76)</f>
-        <v>0.7</v>
-      </c>
-      <c r="C9" s="20">
+        <v>0.85</v>
+      </c>
+      <c r="C9" s="18">
         <v>1</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="26">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="25">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A10, User_Responses!$D$2:$D$76)</f>
-        <v>0.8</v>
-      </c>
-      <c r="C10" s="20">
+        <v>0.9</v>
+      </c>
+      <c r="C10" s="18">
         <v>1</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="26">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="25">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A11, User_Responses!$D$2:$D$76)</f>
-        <v>0.45</v>
-      </c>
-      <c r="C11" s="20">
+        <v>0.4</v>
+      </c>
+      <c r="C11" s="18">
         <v>1</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="26">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="25">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A12, User_Responses!$D$2:$D$76)</f>
         <v>0.7</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="18">
         <v>1</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="26">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
@@ -5396,70 +5430,70 @@
       <c r="A13" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="25">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A13, User_Responses!$D$2:$D$76)</f>
-        <v>0.8</v>
-      </c>
-      <c r="C13" s="20">
+        <v>0.75</v>
+      </c>
+      <c r="C13" s="18">
         <v>3</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="26">
         <f t="shared" si="0"/>
-        <v>2.4000000000000004</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="25">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A14, User_Responses!$D$2:$D$76)</f>
-        <v>0.6</v>
-      </c>
-      <c r="C14" s="20">
+        <v>0.7</v>
+      </c>
+      <c r="C14" s="18">
         <v>2</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="26">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="25">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A15, User_Responses!$D$2:$D$76)</f>
-        <v>0.6</v>
-      </c>
-      <c r="C15" s="20">
+        <v>0.7</v>
+      </c>
+      <c r="C15" s="18">
         <v>2</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="26">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="18" x14ac:dyDescent="0.35">
       <c r="B18" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="28">
         <f>SUM(D2:D15)/SUM(C2:C15)</f>
-        <v>0.64827586206896537</v>
+        <v>0.79137931034482734</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="54" x14ac:dyDescent="0.35">
       <c r="B20" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C20" s="3" t="str">
+      <c r="C20" s="29" t="str">
         <f>IF(C18&lt;=40%, "🟢 High Audit Readiness (Clean Report Forecast)", IF(C18&lt;=60%, "🟡 Moderate Readiness (Minor Exceptions Likely)", IF(C18&lt;=80%, "🟠 Low Readiness (Audit Failure / Non-Conformity Risk)", "🔴 Unprepared (Widespread Exceptions Guaranteed)")))</f>
         <v>🟠 Low Readiness (Audit Failure / Non-Conformity Risk)</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C23" t="s">
@@ -5470,7 +5504,7 @@
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="13">
@@ -5481,7 +5515,7 @@
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="17" t="s">
         <v>22</v>
       </c>
       <c r="C25" s="13">
@@ -5492,7 +5526,7 @@
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="17" t="s">
         <v>100</v>
       </c>
       <c r="C26" s="13">
@@ -5503,7 +5537,7 @@
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="17" t="s">
         <v>40</v>
       </c>
       <c r="C27" s="13">
@@ -5514,7 +5548,7 @@
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="17" t="s">
         <v>94</v>
       </c>
       <c r="C28" s="13">
@@ -5525,7 +5559,7 @@
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="17" t="s">
         <v>58</v>
       </c>
       <c r="C29" s="13">
@@ -5536,7 +5570,7 @@
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="17" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="13">
@@ -5547,7 +5581,7 @@
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="17" t="s">
         <v>64</v>
       </c>
       <c r="C31" s="13">
@@ -5558,7 +5592,7 @@
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="17" t="s">
         <v>52</v>
       </c>
       <c r="C32" s="13">
@@ -5568,8 +5602,8 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B33" s="18" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B33" s="17" t="s">
         <v>28</v>
       </c>
       <c r="C33" s="13">
@@ -5579,8 +5613,8 @@
         <v>2.0999999999999996</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B34" s="18" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B34" s="17" t="s">
         <v>82</v>
       </c>
       <c r="C34" s="13">
@@ -5590,8 +5624,8 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B35" s="18" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B35" s="17" t="s">
         <v>88</v>
       </c>
       <c r="C35" s="13">
@@ -5601,8 +5635,8 @@
         <v>2.4000000000000004</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B36" s="18" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B36" s="17" t="s">
         <v>34</v>
       </c>
       <c r="C36" s="13">
@@ -5612,8 +5646,8 @@
         <v>2.4000000000000004</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B37" s="18" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B37" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C37" s="13">
@@ -5623,8 +5657,8 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B38" s="18" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B38" s="17" t="s">
         <v>13</v>
       </c>
       <c r="C38" s="13">
@@ -5634,7 +5668,13 @@
         <v>18.8</v>
       </c>
     </row>
+    <row r="41" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="14" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="0A+ss9WtuCIGH08sx/ennqVA0I88Q8398/WXq5/763t7PBf55flg6ZPQ2LRqrCHzs6Yw3x3OPd1UWIDWDYNa0Q==" saltValue="qjl/m1LnT9ObW3DaHC9mog==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Select Weight" prompt="Select 1 from (1,2,3,4)" sqref="C2:C15" xr:uid="{C7585D9D-7E7D-4094-AB10-9345EED1BEEF}">
       <formula1>"1,2,3"</formula1>
@@ -5650,7 +5690,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C40AB3C-9D76-48CC-B399-D4A50D69AD7B}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="91.21875" customWidth="1"/>
@@ -5659,13 +5699,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="23" t="s">
         <v>108</v>
       </c>
     </row>
@@ -5673,21 +5713,21 @@
       <c r="A2" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="19" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="19" t="s">
         <v>113</v>
       </c>
     </row>
@@ -5695,25 +5735,31 @@
       <c r="A4" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="19" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="21" t="s">
         <v>119</v>
       </c>
     </row>
+    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="30" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="xVwetFOl4mWMEU8TzxvIVK4rmfSrfXmwLNsxMqBl8QrITZI5B9RMH/zcy/0wLXcOKfmkF0hKl9wc0uFaDSUviw==" saltValue="NEccmj7mCe/54ChZaHytHw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
